--- a/tests/summary.xlsx
+++ b/tests/summary.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="20225"/>
+  <workbookPr autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="210" windowWidth="18195" windowHeight="10995"/>
+    <workbookView xWindow="17500" yWindow="4280" windowWidth="26220" windowHeight="15920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="140001" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
+      <mx:ArchID Flags="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
   <si>
     <t>file</t>
   </si>
@@ -48,9 +53,6 @@
     <t>corner weight</t>
   </si>
   <si>
-    <t>easy.txt</t>
-  </si>
-  <si>
     <t>ties</t>
   </si>
   <si>
@@ -145,13 +147,25 @@
   </si>
   <si>
     <t>removed!</t>
+  </si>
+  <si>
+    <t>reduced</t>
+  </si>
+  <si>
+    <t>somehow my test results were lost</t>
+  </si>
+  <si>
+    <t>but I remember defendable winning in each test</t>
+  </si>
+  <si>
+    <t>keeping defendable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +177,22 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -185,8 +215,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -195,7 +229,11 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="5">
+    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -496,22 +534,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="47" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="66.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="66.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -525,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -537,25 +575,25 @@
         <v>1</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>20</v>
       </c>
@@ -566,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <v>8</v>
@@ -594,13 +632,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>20</v>
       </c>
@@ -611,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>10</v>
@@ -639,13 +677,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>20</v>
       </c>
@@ -656,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -684,10 +722,10 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>20</v>
       </c>
@@ -698,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2">
         <v>25</v>
@@ -726,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="E6" s="2"/>
       <c r="F6" s="1">
         <f>SUM(F2:F5)</f>
@@ -744,21 +782,21 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>8</v>
@@ -786,24 +824,24 @@
         <v>2</v>
       </c>
       <c r="M8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -831,24 +869,24 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E10">
         <v>12</v>
@@ -876,21 +914,21 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2">
         <v>25</v>
@@ -918,10 +956,10 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="F12" s="1">
         <f>SUM(F8:F11)</f>
         <v>94</v>
@@ -935,18 +973,18 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -974,24 +1012,24 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1019,24 +1057,24 @@
         <v>2</v>
       </c>
       <c r="M15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E16">
         <v>12</v>
@@ -1064,24 +1102,24 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2">
         <v>25</v>
@@ -1093,7 +1131,7 @@
         <v>21.5</v>
       </c>
       <c r="H17">
-        <f t="shared" ref="H16:H20" si="1">F17-G17</f>
+        <f t="shared" ref="H17:H20" si="1">F17-G17</f>
         <v>2</v>
       </c>
       <c r="I17">
@@ -1109,13 +1147,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="F18" s="1">
         <f>SUM(F14:F17)</f>
         <v>88</v>
@@ -1129,22 +1167,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14">
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -1172,55 +1210,64 @@
         <v>1</v>
       </c>
       <c r="M20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="N20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E22">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E23">
         <v>25</v>
@@ -1228,23 +1275,39 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/tests/summary.xlsx
+++ b/tests/summary.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="20225"/>
-  <workbookPr autoCompressPictures="0"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="17500" yWindow="4280" windowWidth="26220" windowHeight="15920"/>
+    <workbookView xWindow="17505" yWindow="4335" windowWidth="26220" windowHeight="15855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="140001" concurrentCalc="0"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
   <si>
     <t>file</t>
   </si>
@@ -159,6 +159,33 @@
   </si>
   <si>
     <t>keeping defendable</t>
+  </si>
+  <si>
+    <t>undefended defendable and 1-usable</t>
+  </si>
+  <si>
+    <t>undefended defendable vs undefended defendable and 1-usable.txt</t>
+  </si>
+  <si>
+    <t>undefended defendable vs undefended defendable and 1-usable 2.txt</t>
+  </si>
+  <si>
+    <t>undefended defendable vs undefended defendable and 1-usable 3.txt</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>undefended defendable vs undefended defendable and 1-usable 4.txt</t>
+  </si>
+  <si>
+    <t>improves the strength for longer words, decreases for shorter words</t>
+  </si>
+  <si>
+    <t>I'm going to use the 1-usable thing in player0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -533,23 +560,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="47" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="66.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="65.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="66.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -593,7 +620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>20</v>
       </c>
@@ -638,7 +665,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>20</v>
       </c>
@@ -683,7 +710,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>20</v>
       </c>
@@ -725,7 +752,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>20</v>
       </c>
@@ -767,7 +794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E6" s="2"/>
       <c r="F6" s="1">
         <f>SUM(F2:F5)</f>
@@ -782,10 +809,10 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>20</v>
       </c>
@@ -830,7 +857,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20</v>
       </c>
@@ -875,7 +902,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>20</v>
       </c>
@@ -917,7 +944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>20</v>
       </c>
@@ -959,7 +986,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F12" s="1">
         <f>SUM(F8:F11)</f>
         <v>94</v>
@@ -973,7 +1000,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>20</v>
       </c>
@@ -1018,7 +1045,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>20</v>
       </c>
@@ -1063,7 +1090,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>20</v>
       </c>
@@ -1108,7 +1135,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>20</v>
       </c>
@@ -1153,7 +1180,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F18" s="1">
         <f>SUM(F14:F17)</f>
         <v>88</v>
@@ -1167,11 +1194,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1216,7 +1243,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1236,7 +1263,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1256,7 +1283,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1271,6 +1298,190 @@
       </c>
       <c r="E23">
         <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>76</v>
+      </c>
+      <c r="G26">
+        <v>63.5</v>
+      </c>
+      <c r="H26">
+        <f>F26-G26</f>
+        <v>12.5</v>
+      </c>
+      <c r="I26">
+        <v>53</v>
+      </c>
+      <c r="J26">
+        <v>14</v>
+      </c>
+      <c r="K26">
+        <v>6</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>49</v>
+      </c>
+      <c r="N26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>66</v>
+      </c>
+      <c r="G27">
+        <v>66.5</v>
+      </c>
+      <c r="H27">
+        <f>F27-G27</f>
+        <v>-0.5</v>
+      </c>
+      <c r="I27">
+        <v>54</v>
+      </c>
+      <c r="J27">
+        <v>29</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28">
+        <v>25</v>
+      </c>
+      <c r="F28">
+        <f>21+20+22.5</f>
+        <v>63.5</v>
+      </c>
+      <c r="G28">
+        <f>23+26+23.5</f>
+        <v>72.5</v>
+      </c>
+      <c r="H28">
+        <f>F28-G28</f>
+        <v>-9</v>
+      </c>
+      <c r="I28">
+        <f>18+17+19</f>
+        <v>54</v>
+      </c>
+      <c r="J28">
+        <f>10+5+7</f>
+        <v>22</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>5</v>
+      </c>
+      <c r="M28" t="s">
+        <v>47</v>
+      </c>
+      <c r="N28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29">
+        <v>25</v>
+      </c>
+      <c r="F29">
+        <v>27.5</v>
+      </c>
+      <c r="G29">
+        <v>36</v>
+      </c>
+      <c r="H29">
+        <f>F29-G29</f>
+        <v>-8.5</v>
+      </c>
+      <c r="I29">
+        <v>26</v>
+      </c>
+      <c r="J29">
+        <v>19</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>4</v>
+      </c>
+      <c r="M29" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1287,7 +1498,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1301,7 +1512,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>

--- a/tests/summary.xlsx
+++ b/tests/summary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="17505" yWindow="4335" windowWidth="26220" windowHeight="15855"/>
+    <workbookView xWindow="17505" yWindow="4395" windowWidth="26220" windowHeight="15795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="63">
   <si>
     <t>file</t>
   </si>
@@ -186,6 +186,30 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>normal + vulnerability</t>
+  </si>
+  <si>
+    <t>vulnerability 1.txt</t>
+  </si>
+  <si>
+    <t>vulnerability 2.txt</t>
+  </si>
+  <si>
+    <t>vulnerability 3.txt</t>
+  </si>
+  <si>
+    <t>vulnerability 4.txt</t>
+  </si>
+  <si>
+    <t>like 1-usable, increases strength except for shorter words</t>
+  </si>
+  <si>
+    <t>keeping</t>
   </si>
 </sst>
 </file>
@@ -560,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -1482,6 +1506,180 @@
       </c>
       <c r="N29" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>20</v>
+      </c>
+      <c r="B31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31">
+        <v>25</v>
+      </c>
+      <c r="F31">
+        <v>21.5</v>
+      </c>
+      <c r="G31">
+        <v>25</v>
+      </c>
+      <c r="H31">
+        <f>F31-G31</f>
+        <v>-3.5</v>
+      </c>
+      <c r="I31">
+        <v>18</v>
+      </c>
+      <c r="J31">
+        <v>5</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31" t="s">
+        <v>57</v>
+      </c>
+      <c r="N31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32">
+        <v>25</v>
+      </c>
+      <c r="F32">
+        <v>33</v>
+      </c>
+      <c r="G32">
+        <v>36</v>
+      </c>
+      <c r="H32">
+        <f>F32-G32</f>
+        <v>-3</v>
+      </c>
+      <c r="I32">
+        <v>27</v>
+      </c>
+      <c r="J32">
+        <v>9</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33">
+        <v>12</v>
+      </c>
+      <c r="F33">
+        <v>33</v>
+      </c>
+      <c r="G33">
+        <v>36.5</v>
+      </c>
+      <c r="H33">
+        <f>F33-G33</f>
+        <v>-3.5</v>
+      </c>
+      <c r="I33">
+        <v>24</v>
+      </c>
+      <c r="J33">
+        <v>5</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>4</v>
+      </c>
+      <c r="M33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34">
+        <v>8</v>
+      </c>
+      <c r="F34">
+        <v>37</v>
+      </c>
+      <c r="G34">
+        <v>33.5</v>
+      </c>
+      <c r="H34">
+        <f>F34-G34</f>
+        <v>3.5</v>
+      </c>
+      <c r="I34">
+        <v>23</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34">
+        <v>3</v>
+      </c>
+      <c r="M34" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
